--- a/output/pdf_financials_xlsx/HASH.xlsx
+++ b/output/pdf_financials_xlsx/HASH.xlsx
@@ -889,10 +889,10 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>0.261251</v>
+        <v>-0.261251</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>0.086115</v>
+        <v>-0.086115</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>1.040316</v>
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>0.261251</v>
+        <v>-0.261251</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>0.086115</v>
+        <v>-0.086115</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>1.040316</v>
@@ -1038,10 +1038,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.261251</v>
+        <v>-0.261251</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.086115</v>
+        <v>-0.086115</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>1.040316</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>0.261251</v>
+        <v>-0.261251</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>0.086115</v>
+        <v>-0.086115</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>1.040316</v>
@@ -1176,10 +1176,10 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>0.261251</v>
+        <v>-0.261251</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>0.370522</v>
+        <v>0.198292</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>1.088523</v>
@@ -1218,10 +1218,10 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>0</v>
@@ -3979,7 +3979,11 @@
           <t>Prepaids and deposits 8</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>-</t>
@@ -11263,10 +11267,10 @@
         </is>
       </c>
       <c r="E213" s="5" t="n">
-        <v>0.261251</v>
+        <v>-0.261251</v>
       </c>
       <c r="F213" s="5" t="n">
-        <v>0.086115</v>
+        <v>-0.086115</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
@@ -11369,7 +11373,7 @@
         </is>
       </c>
       <c r="E216" s="5" t="n">
-        <v>0.261251</v>
+        <v>-0.261251</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/HASH.xlsx
+++ b/output/pdf_financials_xlsx/HASH.xlsx
@@ -1420,10 +1420,8 @@
           <t xml:space="preserve">    Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B46" s="3" t="n">
+        <v>0.6122069999999999</v>
       </c>
       <c r="C46" s="3" t="n">
         <v>0.232684</v>
@@ -1468,10 +1466,8 @@
           <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
         </is>
       </c>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B48" s="3" t="n">
+        <v>0.6122069999999999</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0.232684</v>
@@ -3515,13 +3511,13 @@
         <v>0</v>
       </c>
       <c r="C139" s="3" t="n">
-        <v>0</v>
+        <v>-0.036425</v>
       </c>
       <c r="D139" s="3" t="n">
-        <v>0</v>
+        <v>-0.247553</v>
       </c>
       <c r="E139" s="3" t="n">
-        <v>0</v>
+        <v>-0.280504</v>
       </c>
     </row>
     <row r="140">
@@ -3534,13 +3530,13 @@
         <v>0</v>
       </c>
       <c r="C140" s="3" t="n">
-        <v>0</v>
+        <v>-0.036425</v>
       </c>
       <c r="D140" s="3" t="n">
-        <v>0</v>
+        <v>-0.247553</v>
       </c>
       <c r="E140" s="3" t="n">
-        <v>0</v>
+        <v>-0.280504</v>
       </c>
     </row>
     <row r="141">
@@ -6837,7 +6833,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E86" s="5" t="n">
@@ -7925,7 +7921,11 @@
           <t>Lease payments 10</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>-</t>
@@ -8715,7 +8715,11 @@
           <t>Lease payments 10</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E140" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/HASH.xlsx
+++ b/output/pdf_financials_xlsx/HASH.xlsx
@@ -491,10 +491,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C4" s="3" t="n">
+        <v>0.008611000000000001</v>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
@@ -917,7 +915,7 @@
         <v>-0</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.285426</v>
+        <v>-0.285426</v>
       </c>
     </row>
     <row r="24">
@@ -2232,10 +2230,8 @@
       <c r="D79" s="3" t="n">
         <v>1.880186</v>
       </c>
-      <c r="E79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E79" s="3" t="n">
+        <v>0.383368</v>
       </c>
     </row>
     <row r="80">
@@ -3032,7 +3028,7 @@
         <v>-0.261251</v>
       </c>
       <c r="C114" s="3" t="n">
-        <v>-0.086115</v>
+        <v>-1.683799</v>
       </c>
       <c r="D114" s="3" t="n">
         <v>1.040316</v>
@@ -3187,10 +3183,10 @@
         <v>0</v>
       </c>
       <c r="D122" s="3" t="n">
-        <v>0</v>
+        <v>0.218984</v>
       </c>
       <c r="E122" s="3" t="n">
-        <v>0</v>
+        <v>0.628709</v>
       </c>
     </row>
     <row r="123">
@@ -3241,13 +3237,13 @@
         <v>0</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>0.052386</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>0.024022</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>0.26594</v>
       </c>
     </row>
     <row r="126">
@@ -7349,7 +7345,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>-</t>
@@ -7493,7 +7493,11 @@
           <t>Accretion 17</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>-</t>
@@ -7527,7 +7531,11 @@
           <t>Share based compensation expense 14</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
@@ -8273,7 +8281,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
           <t>-</t>
@@ -8367,7 +8379,11 @@
           <t>Accretion 10</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
           <t>-</t>
@@ -10411,7 +10427,11 @@
           <t>Income tax recovery</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
           <t>-</t>
@@ -11117,7 +11137,11 @@
           <t>INTEREST REVENUES 6</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
       <c r="E209" t="inlineStr">
         <is>
           <t>-</t>
